--- a/files/Plan.xlsx
+++ b/files/Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{733EBFC7-8944-45D8-B0FC-2B9A37E95772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD564B06-4BC4-4649-B141-F6266A180E68}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{733EBFC7-8944-45D8-B0FC-2B9A37E95772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75C01B61-87B5-4D75-803D-1822565DCCD9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{563C961A-BFB9-4F7A-BA15-8C34454DAF79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{563C961A-BFB9-4F7A-BA15-8C34454DAF79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -404,21 +404,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -427,46 +418,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -804,138 +810,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A723AB13-D2F9-4241-810A-2D337061B954}">
   <dimension ref="B1:T18"/>
-  <sheetFormatPr defaultColWidth="13.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
-    <col min="2" max="2" width="70.453125" customWidth="1"/>
-    <col min="3" max="20" width="3.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.44140625" customWidth="1"/>
+    <col min="2" max="2" width="70.44140625" customWidth="1"/>
+    <col min="3" max="20" width="3.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="10"/>
-      <c r="C2" s="14" t="s">
+    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B2" s="20"/>
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="18"/>
+      <c r="E2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="18"/>
+      <c r="G2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="18"/>
+      <c r="I2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="3" t="s">
+      <c r="J2" s="18"/>
+      <c r="K2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3" t="s">
+      <c r="L2" s="18"/>
+      <c r="M2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="3" t="s">
+      <c r="N2" s="18"/>
+      <c r="O2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="3" t="s">
+      <c r="P2" s="18"/>
+      <c r="Q2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="3" t="s">
+      <c r="R2" s="18"/>
+      <c r="S2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="5"/>
-    </row>
-    <row r="3" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="11"/>
-      <c r="C3" s="15">
+      <c r="T2" s="19"/>
+    </row>
+    <row r="3" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="21"/>
+      <c r="C3" s="9">
         <v>1</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="10">
         <v>2</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="10">
         <v>1</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="10">
         <v>2</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="10">
         <v>1</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="10">
         <v>2</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="10">
         <v>1</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="10">
         <v>2</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="10">
         <v>1</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="10">
         <v>2</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="10">
         <v>1</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="10">
         <v>2</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="10">
         <v>1</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="10">
         <v>2</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="10">
         <v>1</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="10">
         <v>2</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="10">
         <v>1</v>
       </c>
-      <c r="T3" s="17">
+      <c r="T3" s="11">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="13"/>
-    </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="8" t="s">
+      <c r="C4" s="12"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="8"/>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -952,14 +958,14 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
-      <c r="T5" s="6"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" s="8" t="s">
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="20"/>
+      <c r="D6" s="14"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -975,14 +981,14 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
-      <c r="T6" s="6"/>
-    </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="8" t="s">
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="20"/>
+      <c r="D7" s="14"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -998,14 +1004,14 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="6"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="8" t="s">
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="20"/>
+      <c r="D8" s="14"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1021,15 +1027,15 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="6"/>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B9" s="8" t="s">
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="14"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -1044,15 +1050,15 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="6"/>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1067,15 +1073,15 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="6"/>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B11" s="8" t="s">
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="E11" s="14"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1090,17 +1096,17 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="6"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B12" s="8" t="s">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="23"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1113,17 +1119,17 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="6"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B13" s="8" t="s">
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="14"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -1136,17 +1142,17 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="6"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B14" s="8" t="s">
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="14"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -1159,10 +1165,10 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="T14" s="6"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B15" s="8" t="s">
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="1"/>
@@ -1170,7 +1176,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1182,10 +1188,10 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="T15" s="6"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B16" s="8" t="s">
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="1"/>
@@ -1205,10 +1211,10 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="T16" s="6"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B17" s="8" t="s">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="1"/>
@@ -1228,30 +1234,30 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
-      <c r="T17" s="6"/>
-    </row>
-    <row r="18" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="9" t="s">
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/files/Plan.xlsx
+++ b/files/Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{733EBFC7-8944-45D8-B0FC-2B9A37E95772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75C01B61-87B5-4D75-803D-1822565DCCD9}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{733EBFC7-8944-45D8-B0FC-2B9A37E95772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B98C8A-250B-442C-B437-12B9304D5DD0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{563C961A-BFB9-4F7A-BA15-8C34454DAF79}"/>
+    <workbookView xWindow="2352" yWindow="924" windowWidth="17268" windowHeight="9372" xr2:uid="{563C961A-BFB9-4F7A-BA15-8C34454DAF79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -448,6 +448,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -464,15 +467,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -819,46 +813,46 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B2" s="20"/>
-      <c r="C2" s="22" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="17" t="s">
+      <c r="D2" s="19"/>
+      <c r="E2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="17" t="s">
+      <c r="F2" s="19"/>
+      <c r="G2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="18"/>
-      <c r="I2" s="17" t="s">
+      <c r="H2" s="19"/>
+      <c r="I2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="18"/>
-      <c r="K2" s="17" t="s">
+      <c r="J2" s="19"/>
+      <c r="K2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="17" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="18"/>
-      <c r="O2" s="17" t="s">
+      <c r="N2" s="19"/>
+      <c r="O2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="17" t="s">
+      <c r="P2" s="19"/>
+      <c r="Q2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="18"/>
-      <c r="S2" s="17" t="s">
+      <c r="R2" s="19"/>
+      <c r="S2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="19"/>
+      <c r="T2" s="20"/>
     </row>
     <row r="3" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="21"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9">
         <v>1</v>
       </c>
@@ -1106,7 +1100,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="23"/>
+      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1128,7 +1122,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="23"/>
+      <c r="F13" s="2"/>
       <c r="G13" s="14"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1151,7 +1145,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="23"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="14"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1177,7 +1171,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="14"/>
-      <c r="I15" s="2"/>
+      <c r="I15" s="14"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -1201,7 +1195,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="J16" s="14"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1225,8 +1219,8 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -1240,9 +1234,9 @@
       <c r="B18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
